--- a/calibration_plots/plot_data_vertebral_mpbart.xlsx
+++ b/calibration_plots/plot_data_vertebral_mpbart.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,65 +368,49 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.5204615384615384</v>
+        <v>0.5389871794871794</v>
       </c>
       <c r="B2">
-        <v>0.5897435897435898</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.6237094017094017</v>
+        <v>0.6751282051282051</v>
       </c>
       <c r="B3">
-        <v>0.6410256410256411</v>
+        <v>0.6730769230769231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.7282631578947368</v>
+        <v>0.8063529411764706</v>
       </c>
       <c r="B4">
-        <v>0.7368421052631579</v>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.8195213675213675</v>
+        <v>0.9235769230769231</v>
       </c>
       <c r="B5">
-        <v>0.9230769230769231</v>
+        <v>0.9423076923076923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.9098803418803418</v>
+        <v>0.9848690476190476</v>
       </c>
       <c r="B6">
-        <v>0.9230769230769231</v>
+        <v>0.9821428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.9746166666666667</v>
+        <v>0.9964255319148936</v>
       </c>
       <c r="B7">
-        <v>0.975</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>0.9907567567567568</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>0.996991452991453</v>
-      </c>
-      <c r="B9">
         <v>1</v>
       </c>
     </row>
